--- a/download/netrent-service-import-template.xlsx
+++ b/download/netrent-service-import-template.xlsx
@@ -397,17 +397,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:K4"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
     <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -427,15 +429,21 @@
         <v>Plan Name</v>
       </c>
       <c r="F1" t="str">
+        <v>Customer ID (CID)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Service ID (SID)</v>
+      </c>
+      <c r="H1" t="str">
         <v>Account ID</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>IP Address</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>IP Type</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>Status</v>
       </c>
     </row>
@@ -456,15 +464,21 @@
         <v>Home 300/100</v>
       </c>
       <c r="F2" t="str">
+        <v>CID-AIS-1001</v>
+      </c>
+      <c r="G2" t="str">
+        <v>SID-880019</v>
+      </c>
+      <c r="H2" t="str">
         <v>AIS-900001</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>10.0.10.5</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>STATIC</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>ACTIVE</v>
       </c>
     </row>
@@ -485,15 +499,21 @@
         <v>True 600/150</v>
       </c>
       <c r="F3" t="str">
+        <v>CID-TRUE-2002</v>
+      </c>
+      <c r="G3" t="str">
+        <v>SID-441203</v>
+      </c>
+      <c r="H3" t="str">
         <v>TRUE-900002</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v/>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>DYNAMIC</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>ACTIVE</v>
       </c>
     </row>
@@ -514,21 +534,27 @@
         <v>3BB 200/50</v>
       </c>
       <c r="F4" t="str">
+        <v>CID-3BB-3003</v>
+      </c>
+      <c r="G4" t="str">
+        <v>SID-772910</v>
+      </c>
+      <c r="H4" t="str">
         <v>3BB-900003</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>10.0.30.2</v>
       </c>
-      <c r="H4" t="str">
+      <c r="J4" t="str">
         <v>STATIC</v>
       </c>
-      <c r="I4" t="str">
+      <c r="K4" t="str">
         <v>PENDING</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
   </ignoredErrors>
 </worksheet>
 </file>